--- a/src/width_txt/Максимальные_значения_определителя_АЦП_№3.xlsx
+++ b/src/width_txt/Максимальные_значения_определителя_АЦП_№3.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="430" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="602" uniqueCount="43">
   <si>
     <t>Row</t>
   </si>
@@ -201,7 +201,7 @@
     <col min="9" max="9" width="15.85546875" customWidth="true"/>
     <col min="10" max="10" width="15.85546875" customWidth="true"/>
     <col min="11" max="11" width="15.85546875" customWidth="true"/>
-    <col min="12" max="12" width="15.85546875" customWidth="true"/>
+    <col min="12" max="12" width="13.85546875" customWidth="true"/>
     <col min="13" max="13" width="15.85546875" customWidth="true"/>
   </cols>
   <sheetData>
@@ -251,40 +251,40 @@
         <v>1</v>
       </c>
       <c r="B2" s="0">
-        <v>37747856032761784</v>
+        <v>749133122544</v>
       </c>
       <c r="C2" s="0">
-        <v>37749560782426456</v>
+        <v>34561948810</v>
       </c>
       <c r="D2" s="0">
-        <v>7.7281368217560908e+19</v>
+        <v>70782871162880</v>
       </c>
       <c r="E2" s="0">
         <v>0</v>
       </c>
       <c r="F2" s="0">
-        <v>1.1791421878849769e+19</v>
+        <v>158943616650</v>
       </c>
       <c r="G2" s="0">
-        <v>3.1161886781004365e+22</v>
+        <v>325516526899200</v>
       </c>
       <c r="H2" s="0">
-        <v>2.6949346980739026e+22</v>
+        <v>325516526899200</v>
       </c>
       <c r="I2" s="0">
-        <v>5.4488030140576458e+21</v>
+        <v>15282011745</v>
       </c>
       <c r="J2" s="0">
-        <v>9.9526316466093251e+24</v>
+        <v>31297560053760</v>
       </c>
       <c r="K2" s="0">
-        <v>1.5051285046647532e+25</v>
+        <v>46719426699855</v>
       </c>
       <c r="L2" s="0">
-        <v>1.1895244772979731e+25</v>
+        <v>26099166001545</v>
       </c>
       <c r="M2" s="0">
-        <v>3.945092517792785e+24</v>
+        <v>18492742785</v>
       </c>
     </row>
     <row r="3">
@@ -292,34 +292,34 @@
         <v>2</v>
       </c>
       <c r="B3" s="0">
-        <v>39326545036592040</v>
+        <v>749499088896</v>
       </c>
       <c r="C3" s="0">
-        <v>30894883491784860</v>
+        <v>34561948810</v>
       </c>
       <c r="D3" s="0">
-        <v>7.7281368217560908e+19</v>
+        <v>70748309214070</v>
       </c>
       <c r="E3" s="0">
         <v>0</v>
       </c>
       <c r="F3" s="0">
-        <v>1.0621569331216183e+19</v>
+        <v>158943616650</v>
       </c>
       <c r="G3" s="0">
-        <v>1.9160338341470465e+22</v>
+        <v>325357583282550</v>
       </c>
       <c r="H3" s="0">
-        <v>2.7791929500671783e+22</v>
+        <v>325516526899200</v>
       </c>
       <c r="I3" s="0">
-        <v>5.4488030140576458e+21</v>
+        <v>15282011745</v>
       </c>
       <c r="J3" s="0">
-        <v>1.0390916048708226e+25</v>
+        <v>31282278042015</v>
       </c>
       <c r="K3" s="0">
-        <v>1.656889434449501e+25</v>
+        <v>41214331406430</v>
       </c>
       <c r="L3" s="0">
         <v>0</v>
@@ -333,31 +333,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="0">
-        <v>37692170559790624</v>
+        <v>749499088896</v>
       </c>
       <c r="C4" s="0">
-        <v>37773683855823968</v>
+        <v>34561948810</v>
       </c>
       <c r="D4" s="0">
-        <v>7.7281368217560908e+19</v>
+        <v>70782871162880</v>
       </c>
       <c r="E4" s="0">
         <v>0</v>
       </c>
       <c r="F4" s="0">
-        <v>1.4922421431122676e+19</v>
+        <v>158943616650</v>
       </c>
       <c r="G4" s="0">
-        <v>2.5845633918704472e+22</v>
+        <v>325516526899200</v>
       </c>
       <c r="H4" s="0">
-        <v>2.6949346980739026e+22</v>
+        <v>325357583282550</v>
       </c>
       <c r="I4" s="0">
-        <v>5.7192332200791822e+21</v>
+        <v>15282011745</v>
       </c>
       <c r="J4" s="0">
-        <v>1.2533527764997966e+25</v>
+        <v>31297560053760</v>
       </c>
       <c r="K4" s="0">
         <v>0</v>
@@ -374,31 +374,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="0">
-        <v>38482988293343232</v>
+        <v>749499088896</v>
       </c>
       <c r="C5" s="0">
-        <v>20615510422335840</v>
+        <v>34561948810</v>
       </c>
       <c r="D5" s="0">
-        <v>6.4601195830011617e+19</v>
+        <v>70748309214070</v>
       </c>
       <c r="E5" s="0">
         <v>0</v>
       </c>
       <c r="F5" s="0">
-        <v>1.4922421431122676e+19</v>
+        <v>158943616650</v>
       </c>
       <c r="G5" s="0">
-        <v>2.9907900060380269e+22</v>
+        <v>325357583282550</v>
       </c>
       <c r="H5" s="0">
-        <v>2.7791929500671783e+22</v>
+        <v>325357583282550</v>
       </c>
       <c r="I5" s="0">
-        <v>5.0833248645252718e+21</v>
+        <v>15282011745</v>
       </c>
       <c r="J5" s="0">
-        <v>1.6158205331455039e+25</v>
+        <v>31282278042015</v>
       </c>
       <c r="K5" s="0">
         <v>0</v>
@@ -415,31 +415,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="0">
-        <v>37766296607277056</v>
+        <v>749133122544</v>
       </c>
       <c r="C6" s="0">
-        <v>37749560782426456</v>
+        <v>34561948810</v>
       </c>
       <c r="D6" s="0">
-        <v>6.4601195830011617e+19</v>
+        <v>70748309214070</v>
       </c>
       <c r="E6" s="0">
         <v>0</v>
       </c>
       <c r="F6" s="0">
-        <v>1.0621569331216183e+19</v>
+        <v>158943616650</v>
       </c>
       <c r="G6" s="0">
-        <v>3.1161886781004365e+22</v>
+        <v>325357583282550</v>
       </c>
       <c r="H6" s="0">
-        <v>2.4335077711261603e+22</v>
+        <v>325516526899200</v>
       </c>
       <c r="I6" s="0">
-        <v>5.7192332200791822e+21</v>
+        <v>12742493400</v>
       </c>
       <c r="J6" s="0">
-        <v>1.0154694889382e+25</v>
+        <v>26083883989800</v>
       </c>
       <c r="K6" s="0">
         <v>0</v>
@@ -456,25 +456,25 @@
         <v>6</v>
       </c>
       <c r="B7" s="0">
-        <v>38482988293343232</v>
+        <v>749499088896</v>
       </c>
       <c r="C7" s="0">
-        <v>37773683855823968</v>
+        <v>33846721520</v>
       </c>
       <c r="D7" s="0">
-        <v>6.4601195830011617e+19</v>
+        <v>70782871162880</v>
       </c>
       <c r="E7" s="0">
         <v>0</v>
       </c>
       <c r="F7" s="0">
-        <v>1.0754266088272028e+19</v>
+        <v>5311780770</v>
       </c>
       <c r="G7" s="0">
-        <v>1.8270155970855739e+22</v>
+        <v>325357583282550</v>
       </c>
       <c r="H7" s="0">
-        <v>2.0850315750794273e+22</v>
+        <v>325516526899200</v>
       </c>
       <c r="I7" s="0">
         <v>0</v>
@@ -497,25 +497,25 @@
         <v>7</v>
       </c>
       <c r="B8" s="0">
-        <v>37692170559790624</v>
+        <v>749499088896</v>
       </c>
       <c r="C8" s="0">
-        <v>37749560782426456</v>
+        <v>34561948810</v>
       </c>
       <c r="D8" s="0">
-        <v>7.7309822024037974e+19</v>
+        <v>70748309214070</v>
       </c>
       <c r="E8" s="0">
         <v>0</v>
       </c>
       <c r="F8" s="0">
-        <v>1.1791421878849765e+19</v>
+        <v>158943616650</v>
       </c>
       <c r="G8" s="0">
-        <v>2.4119349435932036e+22</v>
+        <v>10873215236190</v>
       </c>
       <c r="H8" s="0">
-        <v>2.9414085360364957e+22</v>
+        <v>325357583282550</v>
       </c>
       <c r="I8" s="0">
         <v>0</v>
@@ -538,25 +538,25 @@
         <v>8</v>
       </c>
       <c r="B9" s="0">
-        <v>38482988293343232</v>
+        <v>749499088896</v>
       </c>
       <c r="C9" s="0">
-        <v>37773683855823968</v>
+        <v>34561948810</v>
       </c>
       <c r="D9" s="0">
-        <v>7.7309822024037974e+19</v>
+        <v>70782871162880</v>
       </c>
       <c r="E9" s="0">
         <v>0</v>
       </c>
       <c r="F9" s="0">
-        <v>1.0225174219444765e+19</v>
+        <v>158943616650</v>
       </c>
       <c r="G9" s="0">
-        <v>2.2698487116785798e+22</v>
+        <v>325357583282550</v>
       </c>
       <c r="H9" s="0">
-        <v>2.7597878784137886e+22</v>
+        <v>325357583282550</v>
       </c>
       <c r="I9" s="0">
         <v>0</v>
@@ -579,25 +579,25 @@
         <v>9</v>
       </c>
       <c r="B10" s="0">
-        <v>39326545036592040</v>
+        <v>749499088896</v>
       </c>
       <c r="C10" s="0">
-        <v>30894883491784860</v>
+        <v>34561948810</v>
       </c>
       <c r="D10" s="0">
-        <v>7.7309822024037974e+19</v>
+        <v>70782871162880</v>
       </c>
       <c r="E10" s="0">
         <v>0</v>
       </c>
       <c r="F10" s="0">
-        <v>1.0225174219444765e+19</v>
+        <v>158943616650</v>
       </c>
       <c r="G10" s="0">
-        <v>1.8671268928978191e+22</v>
+        <v>325357583282550</v>
       </c>
       <c r="H10" s="0">
-        <v>2.5533769772156626e+22</v>
+        <v>325516526899200</v>
       </c>
       <c r="I10" s="0">
         <v>0</v>
@@ -620,25 +620,25 @@
         <v>10</v>
       </c>
       <c r="B11" s="0">
-        <v>38482988293343232</v>
+        <v>749133122544</v>
       </c>
       <c r="C11" s="0">
-        <v>37773683855823968</v>
+        <v>34561948810</v>
       </c>
       <c r="D11" s="0">
-        <v>4.0330576311826964e+19</v>
+        <v>70748309214070</v>
       </c>
       <c r="E11" s="0">
         <v>0</v>
       </c>
       <c r="F11" s="0">
-        <v>1.4922421431122678e+19</v>
+        <v>158943616650</v>
       </c>
       <c r="G11" s="0">
-        <v>2.0817200207282555e+22</v>
+        <v>325516526899200</v>
       </c>
       <c r="H11" s="0">
-        <v>2.7597878784137886e+22</v>
+        <v>325516526899200</v>
       </c>
       <c r="I11" s="0">
         <v>0</v>
@@ -661,13 +661,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="0">
-        <v>39326545036592040</v>
+        <v>749133122544</v>
       </c>
       <c r="C12" s="0">
         <v>0</v>
       </c>
       <c r="D12" s="0">
-        <v>4.2014410240720445e+19</v>
+        <v>70782871162880</v>
       </c>
       <c r="E12" s="0">
         <v>0</v>
@@ -676,7 +676,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="0">
-        <v>2.3315693829163934e+22</v>
+        <v>325516526899200</v>
       </c>
       <c r="H12" s="0">
         <v>0</v>
@@ -702,13 +702,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="0">
-        <v>37747856032761784</v>
+        <v>749133122544</v>
       </c>
       <c r="C13" s="0">
         <v>0</v>
       </c>
       <c r="D13" s="0">
-        <v>3.9964297414824296e+19</v>
+        <v>70748309214070</v>
       </c>
       <c r="E13" s="0">
         <v>0</v>
@@ -717,7 +717,7 @@
         <v>0</v>
       </c>
       <c r="G13" s="0">
-        <v>1.7176115946289998e+22</v>
+        <v>325357583282550</v>
       </c>
       <c r="H13" s="0">
         <v>0</v>
@@ -743,13 +743,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="0">
-        <v>39326545036592040</v>
+        <v>749499088896</v>
       </c>
       <c r="C14" s="0">
         <v>0</v>
       </c>
       <c r="D14" s="0">
-        <v>7.7357472468585431e+19</v>
+        <v>70782871162880</v>
       </c>
       <c r="E14" s="0">
         <v>0</v>
@@ -758,7 +758,7 @@
         <v>0</v>
       </c>
       <c r="G14" s="0">
-        <v>3.029251550517903e+22</v>
+        <v>325357583282550</v>
       </c>
       <c r="H14" s="0">
         <v>0</v>
@@ -784,13 +784,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="0">
-        <v>37747856032761784</v>
+        <v>749133122544</v>
       </c>
       <c r="C15" s="0">
         <v>0</v>
       </c>
       <c r="D15" s="0">
-        <v>7.7357472468585431e+19</v>
+        <v>70748309214070</v>
       </c>
       <c r="E15" s="0">
         <v>0</v>
@@ -799,7 +799,7 @@
         <v>0</v>
       </c>
       <c r="G15" s="0">
-        <v>2.4119349435932036e+22</v>
+        <v>10873215236190</v>
       </c>
       <c r="H15" s="0">
         <v>0</v>
@@ -825,13 +825,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="0">
-        <v>38482988293343232</v>
+        <v>749133122544</v>
       </c>
       <c r="C16" s="0">
         <v>0</v>
       </c>
       <c r="D16" s="0">
-        <v>7.7357472468585431e+19</v>
+        <v>70782871162880</v>
       </c>
       <c r="E16" s="0">
         <v>0</v>
@@ -840,7 +840,7 @@
         <v>0</v>
       </c>
       <c r="G16" s="0">
-        <v>2.3315693829163934e+22</v>
+        <v>325357583282550</v>
       </c>
       <c r="H16" s="0">
         <v>0</v>
@@ -866,13 +866,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="0">
-        <v>37747856032761784</v>
+        <v>749499088896</v>
       </c>
       <c r="C17" s="0">
         <v>0</v>
       </c>
       <c r="D17" s="0">
-        <v>7.6875590754621604e+19</v>
+        <v>69318085672960</v>
       </c>
       <c r="E17" s="0">
         <v>0</v>
@@ -881,7 +881,7 @@
         <v>0</v>
       </c>
       <c r="G17" s="0">
-        <v>3.0270542681486366e+22</v>
+        <v>325357583282550</v>
       </c>
       <c r="H17" s="0">
         <v>0</v>
@@ -907,13 +907,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="0">
-        <v>38482988293343232</v>
+        <v>749499088896</v>
       </c>
       <c r="C18" s="0">
         <v>0</v>
       </c>
       <c r="D18" s="0">
-        <v>7.6756190333601366e+19</v>
+        <v>69318085672960</v>
       </c>
       <c r="E18" s="0">
         <v>0</v>
@@ -922,7 +922,7 @@
         <v>0</v>
       </c>
       <c r="G18" s="0">
-        <v>3.029251550517903e+22</v>
+        <v>325357583282550</v>
       </c>
       <c r="H18" s="0">
         <v>0</v>
@@ -948,13 +948,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="0">
-        <v>36393312275092288</v>
+        <v>749499088896</v>
       </c>
       <c r="C19" s="0">
         <v>0</v>
       </c>
       <c r="D19" s="0">
-        <v>7.7215080605844161e+19</v>
+        <v>69318085672960</v>
       </c>
       <c r="E19" s="0">
         <v>0</v>
@@ -963,7 +963,7 @@
         <v>0</v>
       </c>
       <c r="G19" s="0">
-        <v>2.3665383710851479e+22</v>
+        <v>325516526899200</v>
       </c>
       <c r="H19" s="0">
         <v>0</v>
@@ -989,13 +989,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="0">
-        <v>37747856032761784</v>
+        <v>749499088896</v>
       </c>
       <c r="C20" s="0">
         <v>0</v>
       </c>
       <c r="D20" s="0">
-        <v>7.6675484701287121e+19</v>
+        <v>70782871162880</v>
       </c>
       <c r="E20" s="0">
         <v>0</v>
@@ -1004,7 +1004,7 @@
         <v>0</v>
       </c>
       <c r="G20" s="0">
-        <v>1.8342997559766447e+22</v>
+        <v>325357583282550</v>
       </c>
       <c r="H20" s="0">
         <v>0</v>
@@ -1030,13 +1030,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="0">
-        <v>37766296607277056</v>
+        <v>749133122544</v>
       </c>
       <c r="C21" s="0">
         <v>0</v>
       </c>
       <c r="D21" s="0">
-        <v>7.6675484701287121e+19</v>
+        <v>70782871162880</v>
       </c>
       <c r="E21" s="0">
         <v>0</v>
@@ -1045,7 +1045,7 @@
         <v>0</v>
       </c>
       <c r="G21" s="0">
-        <v>3.0270542681486366e+22</v>
+        <v>325516526899200</v>
       </c>
       <c r="H21" s="0">
         <v>0</v>
@@ -1077,7 +1077,7 @@
         <v>0</v>
       </c>
       <c r="D22" s="0">
-        <v>7.727335092162696e+19</v>
+        <v>70748309214070</v>
       </c>
       <c r="E22" s="0">
         <v>0</v>
@@ -1118,7 +1118,7 @@
         <v>0</v>
       </c>
       <c r="D23" s="0">
-        <v>7.7354964550451347e+19</v>
+        <v>70782871162880</v>
       </c>
       <c r="E23" s="0">
         <v>0</v>
@@ -1159,7 +1159,7 @@
         <v>0</v>
       </c>
       <c r="D24" s="0">
-        <v>7.7354964550451347e+19</v>
+        <v>70748309214070</v>
       </c>
       <c r="E24" s="0">
         <v>0</v>
@@ -1200,7 +1200,7 @@
         <v>0</v>
       </c>
       <c r="D25" s="0">
-        <v>7.7354964550451347e+19</v>
+        <v>70782871162880</v>
       </c>
       <c r="E25" s="0">
         <v>0</v>
@@ -1241,7 +1241,7 @@
         <v>0</v>
       </c>
       <c r="D26" s="0">
-        <v>6.1906636932407894e+19</v>
+        <v>70782871162880</v>
       </c>
       <c r="E26" s="0">
         <v>0</v>
@@ -1282,7 +1282,7 @@
         <v>0</v>
       </c>
       <c r="D27" s="0">
-        <v>6.1906636932407894e+19</v>
+        <v>70748309214070</v>
       </c>
       <c r="E27" s="0">
         <v>0</v>
@@ -1323,7 +1323,7 @@
         <v>0</v>
       </c>
       <c r="D28" s="0">
-        <v>6.1906636932407894e+19</v>
+        <v>70748309214070</v>
       </c>
       <c r="E28" s="0">
         <v>0</v>
@@ -1364,7 +1364,7 @@
         <v>0</v>
       </c>
       <c r="D29" s="0">
-        <v>7.6875590754621604e+19</v>
+        <v>70782871162880</v>
       </c>
       <c r="E29" s="0">
         <v>0</v>
@@ -1405,7 +1405,7 @@
         <v>0</v>
       </c>
       <c r="D30" s="0">
-        <v>7.6705192466831229e+19</v>
+        <v>70748309214070</v>
       </c>
       <c r="E30" s="0">
         <v>0</v>
@@ -1446,7 +1446,7 @@
         <v>0</v>
       </c>
       <c r="D31" s="0">
-        <v>7.6756190333601366e+19</v>
+        <v>70782871162880</v>
       </c>
       <c r="E31" s="0">
         <v>0</v>

--- a/src/width_txt/Максимальные_значения_определителя_АЦП_№3.xlsx
+++ b/src/width_txt/Максимальные_значения_определителя_АЦП_№3.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="602" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="2752" uniqueCount="43">
   <si>
     <t>Row</t>
   </si>
@@ -191,17 +191,17 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="true"/>
-    <col min="2" max="2" width="15.85546875" customWidth="true"/>
-    <col min="3" max="3" width="15.85546875" customWidth="true"/>
-    <col min="4" max="4" width="15.85546875" customWidth="true"/>
+    <col min="2" max="2" width="14.85546875" customWidth="true"/>
+    <col min="3" max="3" width="11.42578125" customWidth="true"/>
+    <col min="4" max="4" width="14.85546875" customWidth="true"/>
     <col min="5" max="5" width="12.85546875" customWidth="true"/>
-    <col min="6" max="6" width="15.85546875" customWidth="true"/>
+    <col min="6" max="6" width="10.140625" customWidth="true"/>
     <col min="7" max="7" width="15.85546875" customWidth="true"/>
     <col min="8" max="8" width="15.85546875" customWidth="true"/>
-    <col min="9" max="9" width="15.85546875" customWidth="true"/>
+    <col min="9" max="9" width="11.140625" customWidth="true"/>
     <col min="10" max="10" width="15.85546875" customWidth="true"/>
     <col min="11" max="11" width="15.85546875" customWidth="true"/>
-    <col min="12" max="12" width="13.85546875" customWidth="true"/>
+    <col min="12" max="12" width="15.85546875" customWidth="true"/>
     <col min="13" max="13" width="15.85546875" customWidth="true"/>
   </cols>
   <sheetData>
@@ -251,40 +251,40 @@
         <v>1</v>
       </c>
       <c r="B2" s="0">
-        <v>749133122544</v>
+        <v>3983756</v>
       </c>
       <c r="C2" s="0">
-        <v>34561948810</v>
+        <v>1491348</v>
       </c>
       <c r="D2" s="0">
-        <v>70782871162880</v>
+        <v>3052789356</v>
       </c>
       <c r="E2" s="0">
-        <v>0</v>
+        <v>1599452699</v>
       </c>
       <c r="F2" s="0">
-        <v>158943616650</v>
+        <v>569070768</v>
       </c>
       <c r="G2" s="0">
-        <v>325516526899200</v>
+        <v>364466163690</v>
       </c>
       <c r="H2" s="0">
-        <v>325516526899200</v>
+        <v>740441819683</v>
       </c>
       <c r="I2" s="0">
-        <v>15282011745</v>
+        <v>3129211136</v>
       </c>
       <c r="J2" s="0">
-        <v>31297560053760</v>
+        <v>6092574081792</v>
       </c>
       <c r="K2" s="0">
-        <v>46719426699855</v>
+        <v>5421229759642</v>
       </c>
       <c r="L2" s="0">
-        <v>26099166001545</v>
+        <v>10218150322758</v>
       </c>
       <c r="M2" s="0">
-        <v>18492742785</v>
+        <v>33043182888</v>
       </c>
     </row>
     <row r="3">
@@ -292,34 +292,34 @@
         <v>2</v>
       </c>
       <c r="B3" s="0">
-        <v>749499088896</v>
+        <v>4227055</v>
       </c>
       <c r="C3" s="0">
-        <v>34561948810</v>
+        <v>2376622</v>
       </c>
       <c r="D3" s="0">
-        <v>70748309214070</v>
+        <v>2471163636</v>
       </c>
       <c r="E3" s="0">
-        <v>0</v>
+        <v>1859259031</v>
       </c>
       <c r="F3" s="0">
-        <v>158943616650</v>
+        <v>577917001</v>
       </c>
       <c r="G3" s="0">
-        <v>325357583282550</v>
+        <v>964007803000</v>
       </c>
       <c r="H3" s="0">
-        <v>325516526899200</v>
+        <v>742236967620</v>
       </c>
       <c r="I3" s="0">
-        <v>15282011745</v>
+        <v>3958720682</v>
       </c>
       <c r="J3" s="0">
-        <v>31282278042015</v>
+        <v>4891804286976</v>
       </c>
       <c r="K3" s="0">
-        <v>41214331406430</v>
+        <v>8307175807427</v>
       </c>
       <c r="L3" s="0">
         <v>0</v>
@@ -333,31 +333,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="0">
-        <v>749499088896</v>
+        <v>3983756</v>
       </c>
       <c r="C4" s="0">
-        <v>34561948810</v>
+        <v>2368015</v>
       </c>
       <c r="D4" s="0">
-        <v>70782871162880</v>
+        <v>944636542</v>
       </c>
       <c r="E4" s="0">
-        <v>0</v>
+        <v>2051578134</v>
       </c>
       <c r="F4" s="0">
-        <v>158943616650</v>
+        <v>581779000</v>
       </c>
       <c r="G4" s="0">
-        <v>325516526899200</v>
+        <v>1190319834000</v>
       </c>
       <c r="H4" s="0">
-        <v>325357583282550</v>
+        <v>1161240764026</v>
       </c>
       <c r="I4" s="0">
-        <v>15282011745</v>
+        <v>5071925138</v>
       </c>
       <c r="J4" s="0">
-        <v>31297560053760</v>
+        <v>3761311785472</v>
       </c>
       <c r="K4" s="0">
         <v>0</v>
@@ -374,31 +374,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="0">
-        <v>749499088896</v>
+        <v>3993697</v>
       </c>
       <c r="C5" s="0">
-        <v>34561948810</v>
+        <v>1599160</v>
       </c>
       <c r="D5" s="0">
-        <v>70748309214070</v>
+        <v>3945192520</v>
       </c>
       <c r="E5" s="0">
-        <v>0</v>
+        <v>1751279898</v>
       </c>
       <c r="F5" s="0">
-        <v>158943616650</v>
+        <v>569127874</v>
       </c>
       <c r="G5" s="0">
-        <v>325357583282550</v>
+        <v>957030553656</v>
       </c>
       <c r="H5" s="0">
-        <v>325357583282550</v>
+        <v>1160047562100</v>
       </c>
       <c r="I5" s="0">
-        <v>15282011745</v>
+        <v>5071925138</v>
       </c>
       <c r="J5" s="0">
-        <v>31282278042015</v>
+        <v>8404179953666</v>
       </c>
       <c r="K5" s="0">
         <v>0</v>
@@ -415,31 +415,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="0">
-        <v>749133122544</v>
+        <v>3983756</v>
       </c>
       <c r="C6" s="0">
-        <v>34561948810</v>
+        <v>2376622</v>
       </c>
       <c r="D6" s="0">
-        <v>70748309214070</v>
+        <v>3938062654</v>
       </c>
       <c r="E6" s="0">
-        <v>0</v>
+        <v>2051578134</v>
       </c>
       <c r="F6" s="0">
-        <v>158943616650</v>
+        <v>575775930</v>
       </c>
       <c r="G6" s="0">
-        <v>325357583282550</v>
+        <v>366193491480</v>
       </c>
       <c r="H6" s="0">
-        <v>325516526899200</v>
+        <v>727813156878</v>
       </c>
       <c r="I6" s="0">
-        <v>12742493400</v>
+        <v>4987944388</v>
       </c>
       <c r="J6" s="0">
-        <v>26083883989800</v>
+        <v>10205334217848</v>
       </c>
       <c r="K6" s="0">
         <v>0</v>
@@ -456,25 +456,25 @@
         <v>6</v>
       </c>
       <c r="B7" s="0">
-        <v>749499088896</v>
+        <v>3989603</v>
       </c>
       <c r="C7" s="0">
-        <v>33846721520</v>
+        <v>2368015</v>
       </c>
       <c r="D7" s="0">
-        <v>70782871162880</v>
+        <v>1504401726</v>
       </c>
       <c r="E7" s="0">
-        <v>0</v>
+        <v>2051578134</v>
       </c>
       <c r="F7" s="0">
-        <v>5311780770</v>
+        <v>569127874</v>
       </c>
       <c r="G7" s="0">
-        <v>325357583282550</v>
+        <v>943044887218</v>
       </c>
       <c r="H7" s="0">
-        <v>325516526899200</v>
+        <v>722825212490</v>
       </c>
       <c r="I7" s="0">
         <v>0</v>
@@ -497,25 +497,25 @@
         <v>7</v>
       </c>
       <c r="B8" s="0">
-        <v>749499088896</v>
+        <v>3983756</v>
       </c>
       <c r="C8" s="0">
-        <v>34561948810</v>
+        <v>2354589</v>
       </c>
       <c r="D8" s="0">
-        <v>70748309214070</v>
+        <v>3923800855</v>
       </c>
       <c r="E8" s="0">
-        <v>0</v>
+        <v>3975903119</v>
       </c>
       <c r="F8" s="0">
-        <v>158943616650</v>
+        <v>577917001</v>
       </c>
       <c r="G8" s="0">
-        <v>10873215236190</v>
+        <v>1178037552780</v>
       </c>
       <c r="H8" s="0">
-        <v>325357583282550</v>
+        <v>593044706232</v>
       </c>
       <c r="I8" s="0">
         <v>0</v>
@@ -538,25 +538,25 @@
         <v>8</v>
       </c>
       <c r="B9" s="0">
-        <v>749499088896</v>
+        <v>3989603</v>
       </c>
       <c r="C9" s="0">
-        <v>34561948810</v>
+        <v>2376622</v>
       </c>
       <c r="D9" s="0">
-        <v>70782871162880</v>
+        <v>4844958690</v>
       </c>
       <c r="E9" s="0">
-        <v>0</v>
+        <v>3975903119</v>
       </c>
       <c r="F9" s="0">
-        <v>158943616650</v>
+        <v>581779000</v>
       </c>
       <c r="G9" s="0">
-        <v>325357583282550</v>
+        <v>942475759344</v>
       </c>
       <c r="H9" s="0">
-        <v>325357583282550</v>
+        <v>588793842874</v>
       </c>
       <c r="I9" s="0">
         <v>0</v>
@@ -579,25 +579,25 @@
         <v>9</v>
       </c>
       <c r="B10" s="0">
-        <v>749499088896</v>
+        <v>4227055</v>
       </c>
       <c r="C10" s="0">
-        <v>34561948810</v>
+        <v>2376622</v>
       </c>
       <c r="D10" s="0">
-        <v>70782871162880</v>
+        <v>1757820480</v>
       </c>
       <c r="E10" s="0">
-        <v>0</v>
+        <v>3969631456</v>
       </c>
       <c r="F10" s="0">
-        <v>158943616650</v>
+        <v>581779000</v>
       </c>
       <c r="G10" s="0">
-        <v>325357583282550</v>
+        <v>449136011088</v>
       </c>
       <c r="H10" s="0">
-        <v>325516526899200</v>
+        <v>727813156878</v>
       </c>
       <c r="I10" s="0">
         <v>0</v>
@@ -620,25 +620,25 @@
         <v>10</v>
       </c>
       <c r="B11" s="0">
-        <v>749133122544</v>
+        <v>3978089</v>
       </c>
       <c r="C11" s="0">
-        <v>34561948810</v>
+        <v>2368015</v>
       </c>
       <c r="D11" s="0">
-        <v>70748309214070</v>
+        <v>2649808120</v>
       </c>
       <c r="E11" s="0">
-        <v>0</v>
+        <v>4854988958</v>
       </c>
       <c r="F11" s="0">
-        <v>158943616650</v>
+        <v>575775930</v>
       </c>
       <c r="G11" s="0">
-        <v>325516526899200</v>
+        <v>406294736776</v>
       </c>
       <c r="H11" s="0">
-        <v>325516526899200</v>
+        <v>722825212490</v>
       </c>
       <c r="I11" s="0">
         <v>0</v>
@@ -661,13 +661,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="0">
-        <v>749133122544</v>
+        <v>4227055</v>
       </c>
       <c r="C12" s="0">
         <v>0</v>
       </c>
       <c r="D12" s="0">
-        <v>70782871162880</v>
+        <v>3271881360</v>
       </c>
       <c r="E12" s="0">
         <v>0</v>
@@ -676,7 +676,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="0">
-        <v>325516526899200</v>
+        <v>1190319834000</v>
       </c>
       <c r="H12" s="0">
         <v>0</v>
@@ -702,13 +702,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="0">
-        <v>749133122544</v>
+        <v>3792754</v>
       </c>
       <c r="C13" s="0">
         <v>0</v>
       </c>
       <c r="D13" s="0">
-        <v>70748309214070</v>
+        <v>2648208960</v>
       </c>
       <c r="E13" s="0">
         <v>0</v>
@@ -717,7 +717,7 @@
         <v>0</v>
       </c>
       <c r="G13" s="0">
-        <v>325357583282550</v>
+        <v>957030553656</v>
       </c>
       <c r="H13" s="0">
         <v>0</v>
@@ -743,13 +743,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="0">
-        <v>749499088896</v>
+        <v>4227055</v>
       </c>
       <c r="C14" s="0">
         <v>0</v>
       </c>
       <c r="D14" s="0">
-        <v>70782871162880</v>
+        <v>1509154970</v>
       </c>
       <c r="E14" s="0">
         <v>0</v>
@@ -758,7 +758,7 @@
         <v>0</v>
       </c>
       <c r="G14" s="0">
-        <v>325357583282550</v>
+        <v>449136011088</v>
       </c>
       <c r="H14" s="0">
         <v>0</v>
@@ -784,13 +784,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="0">
-        <v>749133122544</v>
+        <v>3792754</v>
       </c>
       <c r="C15" s="0">
         <v>0</v>
       </c>
       <c r="D15" s="0">
-        <v>70748309214070</v>
+        <v>3938062654</v>
       </c>
       <c r="E15" s="0">
         <v>0</v>
@@ -799,7 +799,7 @@
         <v>0</v>
       </c>
       <c r="G15" s="0">
-        <v>10873215236190</v>
+        <v>406294736776</v>
       </c>
       <c r="H15" s="0">
         <v>0</v>
@@ -825,13 +825,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="0">
-        <v>749133122544</v>
+        <v>3978089</v>
       </c>
       <c r="C16" s="0">
         <v>0</v>
       </c>
       <c r="D16" s="0">
-        <v>70782871162880</v>
+        <v>1504401726</v>
       </c>
       <c r="E16" s="0">
         <v>0</v>
@@ -840,7 +840,7 @@
         <v>0</v>
       </c>
       <c r="G16" s="0">
-        <v>325357583282550</v>
+        <v>964007803000</v>
       </c>
       <c r="H16" s="0">
         <v>0</v>
@@ -866,13 +866,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="0">
-        <v>749499088896</v>
+        <v>3384864</v>
       </c>
       <c r="C17" s="0">
         <v>0</v>
       </c>
       <c r="D17" s="0">
-        <v>69318085672960</v>
+        <v>1746409392</v>
       </c>
       <c r="E17" s="0">
         <v>0</v>
@@ -881,7 +881,7 @@
         <v>0</v>
       </c>
       <c r="G17" s="0">
-        <v>325357583282550</v>
+        <v>942381191808</v>
       </c>
       <c r="H17" s="0">
         <v>0</v>
@@ -907,13 +907,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="0">
-        <v>749499088896</v>
+        <v>3978089</v>
       </c>
       <c r="C18" s="0">
         <v>0</v>
       </c>
       <c r="D18" s="0">
-        <v>69318085672960</v>
+        <v>4844958690</v>
       </c>
       <c r="E18" s="0">
         <v>0</v>
@@ -922,7 +922,7 @@
         <v>0</v>
       </c>
       <c r="G18" s="0">
-        <v>325357583282550</v>
+        <v>367555212636</v>
       </c>
       <c r="H18" s="0">
         <v>0</v>
@@ -948,13 +948,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="0">
-        <v>749499088896</v>
+        <v>3227544</v>
       </c>
       <c r="C19" s="0">
         <v>0</v>
       </c>
       <c r="D19" s="0">
-        <v>69318085672960</v>
+        <v>1747462080</v>
       </c>
       <c r="E19" s="0">
         <v>0</v>
@@ -963,7 +963,7 @@
         <v>0</v>
       </c>
       <c r="G19" s="0">
-        <v>325516526899200</v>
+        <v>360257944242</v>
       </c>
       <c r="H19" s="0">
         <v>0</v>
@@ -989,13 +989,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="0">
-        <v>749499088896</v>
+        <v>3384864</v>
       </c>
       <c r="C20" s="0">
         <v>0</v>
       </c>
       <c r="D20" s="0">
-        <v>70782871162880</v>
+        <v>2051916480</v>
       </c>
       <c r="E20" s="0">
         <v>0</v>
@@ -1004,7 +1004,7 @@
         <v>0</v>
       </c>
       <c r="G20" s="0">
-        <v>325357583282550</v>
+        <v>957608470657</v>
       </c>
       <c r="H20" s="0">
         <v>0</v>
@@ -1030,13 +1030,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="0">
-        <v>749133122544</v>
+        <v>2755600</v>
       </c>
       <c r="C21" s="0">
         <v>0</v>
       </c>
       <c r="D21" s="0">
-        <v>70782871162880</v>
+        <v>4822198272</v>
       </c>
       <c r="E21" s="0">
         <v>0</v>
@@ -1045,7 +1045,7 @@
         <v>0</v>
       </c>
       <c r="G21" s="0">
-        <v>325516526899200</v>
+        <v>1164318791328</v>
       </c>
       <c r="H21" s="0">
         <v>0</v>
@@ -1077,7 +1077,7 @@
         <v>0</v>
       </c>
       <c r="D22" s="0">
-        <v>70748309214070</v>
+        <v>3896584545</v>
       </c>
       <c r="E22" s="0">
         <v>0</v>
@@ -1118,7 +1118,7 @@
         <v>0</v>
       </c>
       <c r="D23" s="0">
-        <v>70782871162880</v>
+        <v>1746409392</v>
       </c>
       <c r="E23" s="0">
         <v>0</v>
@@ -1159,7 +1159,7 @@
         <v>0</v>
       </c>
       <c r="D24" s="0">
-        <v>70748309214070</v>
+        <v>3945192520</v>
       </c>
       <c r="E24" s="0">
         <v>0</v>
@@ -1200,7 +1200,7 @@
         <v>0</v>
       </c>
       <c r="D25" s="0">
-        <v>70782871162880</v>
+        <v>1747462080</v>
       </c>
       <c r="E25" s="0">
         <v>0</v>
@@ -1241,7 +1241,7 @@
         <v>0</v>
       </c>
       <c r="D26" s="0">
-        <v>70782871162880</v>
+        <v>2051916480</v>
       </c>
       <c r="E26" s="0">
         <v>0</v>
@@ -1282,7 +1282,7 @@
         <v>0</v>
       </c>
       <c r="D27" s="0">
-        <v>70748309214070</v>
+        <v>3945192520</v>
       </c>
       <c r="E27" s="0">
         <v>0</v>
@@ -1323,7 +1323,7 @@
         <v>0</v>
       </c>
       <c r="D28" s="0">
-        <v>70748309214070</v>
+        <v>3938062654</v>
       </c>
       <c r="E28" s="0">
         <v>0</v>
@@ -1364,7 +1364,7 @@
         <v>0</v>
       </c>
       <c r="D29" s="0">
-        <v>70782871162880</v>
+        <v>2051916480</v>
       </c>
       <c r="E29" s="0">
         <v>0</v>
@@ -1405,7 +1405,7 @@
         <v>0</v>
       </c>
       <c r="D30" s="0">
-        <v>70748309214070</v>
+        <v>3923800855</v>
       </c>
       <c r="E30" s="0">
         <v>0</v>
@@ -1446,7 +1446,7 @@
         <v>0</v>
       </c>
       <c r="D31" s="0">
-        <v>70782871162880</v>
+        <v>4844958690</v>
       </c>
       <c r="E31" s="0">
         <v>0</v>
